--- a/STATS_2026.xlsx
+++ b/STATS_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="EXP" sheetId="1" r:id="rId1"/>
@@ -7783,60 +7783,60 @@
         <v>36</v>
       </c>
       <c r="C80" s="6">
-        <f>SUM(C3:C49)</f>
-        <v>524</v>
+        <f>SUM(C3:C78)</f>
+        <v>529</v>
       </c>
       <c r="D80" s="6">
-        <f t="shared" ref="D80:U80" si="2">SUM(D3:D49)</f>
-        <v>7053</v>
+        <f t="shared" ref="D80:U80" si="2">SUM(D3:D78)</f>
+        <v>7097</v>
       </c>
       <c r="E80" s="6">
         <f t="shared" si="2"/>
-        <v>6770</v>
+        <v>6805</v>
       </c>
       <c r="F80" s="6">
         <f t="shared" si="2"/>
-        <v>2588</v>
+        <v>2602</v>
       </c>
       <c r="G80" s="6">
         <f t="shared" si="2"/>
-        <v>5489</v>
+        <v>5524</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="2"/>
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="2"/>
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="2"/>
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="2"/>
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="2"/>
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="2"/>
-        <v>2155</v>
+        <v>2168</v>
       </c>
       <c r="N80" s="6">
         <f t="shared" si="2"/>
-        <v>2689</v>
+        <v>2707</v>
       </c>
       <c r="O80" s="6">
         <f t="shared" si="2"/>
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="P80" s="6">
         <f t="shared" si="2"/>
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q80" s="6">
         <f t="shared" si="2"/>
@@ -7844,19 +7844,19 @@
       </c>
       <c r="R80" s="6">
         <f t="shared" si="2"/>
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="S80" s="6">
         <f t="shared" si="2"/>
-        <v>1275</v>
+        <v>1287</v>
       </c>
       <c r="T80" s="6">
         <f t="shared" si="2"/>
-        <v>2018</v>
+        <v>2028</v>
       </c>
       <c r="U80" s="6">
         <f t="shared" si="2"/>
-        <v>3759</v>
+        <v>3780</v>
       </c>
       <c r="V80" s="6"/>
       <c r="W80" s="6"/>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="C81" s="9">
         <f>100*(E80)/(2*(G80+0.44*K80))</f>
-        <v>58.250789870385539</v>
+        <v>58.179498929599816</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="C82" s="6">
         <f>(E80)/((G80+0.44*K80+R80))</f>
-        <v>1.0378532840314698</v>
+        <v>1.036513294177857</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C83" s="9">
         <f>100*(H80/I80)</f>
-        <v>32.947976878612714</v>
+        <v>32.912844036697244</v>
       </c>
     </row>
     <row r="84" spans="2:31">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="C84" s="9">
         <f>100*(T80/U80)</f>
-        <v>53.684490555998934</v>
+        <v>53.650793650793652</v>
       </c>
     </row>
     <row r="85" spans="2:31">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="C85" s="9">
         <f>100*(F80/G80)</f>
-        <v>47.148843140827104</v>
+        <v>47.103548153511952</v>
       </c>
     </row>
     <row r="86" spans="2:31">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="C86" s="9">
         <f>100*(F80+0.5*H80)/(G80)</f>
-        <v>52.341045727819278</v>
+        <v>52.299058653149892</v>
       </c>
     </row>
     <row r="87" spans="2:31">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="C87" s="9">
         <f>100*(J80/K80)</f>
-        <v>77.322404371584696</v>
+        <v>77.06919945725916</v>
       </c>
     </row>
   </sheetData>
@@ -8608,19 +8608,19 @@
       </c>
       <c r="AE3" s="4">
         <f>100*(AA3/TOTAL_BASIC!$C$81)</f>
-        <v>112.14674570606115</v>
+        <v>112.28416605437177</v>
       </c>
       <c r="AF3" s="4">
         <f>100*AC3/TOTAL_BASIC!$C$82</f>
-        <v>111.07857847630501</v>
+        <v>111.22217930511064</v>
       </c>
       <c r="AG3" s="4">
         <f>100*N3/TOTAL_BASIC!$C$87</f>
-        <v>119.37031802120141</v>
+        <v>119.7625</v>
       </c>
       <c r="AH3" s="4">
         <f>100*AD3/TOTAL_BASIC!$C$86</f>
-        <v>109.33184985181948</v>
+        <v>109.41962436749317</v>
       </c>
       <c r="AI3" s="3">
         <f>T3/V3</f>
@@ -8848,19 +8848,19 @@
       </c>
       <c r="AE4" s="4">
         <f>100*(AA4/TOTAL_BASIC!$C$81)</f>
-        <v>115.00929787673506</v>
+        <v>115.15022588738464</v>
       </c>
       <c r="AF4" s="4">
         <f>100*AC4/TOTAL_BASIC!$C$82</f>
-        <v>112.37144381117446</v>
+        <v>112.51671603815755</v>
       </c>
       <c r="AG4" s="4">
         <f>100*N4/TOTAL_BASIC!$C$87</f>
-        <v>123.76749116607775</v>
+        <v>124.17411971830985</v>
       </c>
       <c r="AH4" s="4">
         <f>100*AD4/TOTAL_BASIC!$C$86</f>
-        <v>114.3014793905386</v>
+        <v>114.39324365692474</v>
       </c>
       <c r="AI4" s="3">
         <f t="shared" ref="AI4:AI54" si="36">T4/V4</f>
@@ -9088,19 +9088,19 @@
       </c>
       <c r="AE5" s="4">
         <f>100*(AA5/TOTAL_BASIC!$C$81)</f>
-        <v>92.929353234891664</v>
+        <v>93.043225322836946</v>
       </c>
       <c r="AF5" s="4">
         <f>100*AC5/TOTAL_BASIC!$C$82</f>
-        <v>90.091381621334946</v>
+        <v>90.20785049631094</v>
       </c>
       <c r="AG5" s="4">
         <f>100*N5/TOTAL_BASIC!$C$87</f>
-        <v>102.42826855123676</v>
+        <v>102.76478873239436</v>
       </c>
       <c r="AH5" s="4">
         <f>100*AD5/TOTAL_BASIC!$C$86</f>
-        <v>95.527323355377646</v>
+        <v>95.60401523018345</v>
       </c>
       <c r="AI5" s="3">
         <f t="shared" si="36"/>
@@ -9328,19 +9328,19 @@
       </c>
       <c r="AE6" s="4">
         <f>100*(AA6/TOTAL_BASIC!$C$81)</f>
-        <v>105.99428951863538</v>
+        <v>106.12417088160213</v>
       </c>
       <c r="AF6" s="4">
         <f>100*AC6/TOTAL_BASIC!$C$82</f>
-        <v>109.01000550548832</v>
+        <v>109.15093211216103</v>
       </c>
       <c r="AG6" s="4">
         <f>100*N6/TOTAL_BASIC!$C$87</f>
-        <v>117.55971731448764</v>
+        <v>117.94595070422535</v>
       </c>
       <c r="AH6" s="4">
         <f>100*AD6/TOTAL_BASIC!$C$86</f>
-        <v>108.11176116267291</v>
+        <v>108.19855615871062</v>
       </c>
       <c r="AI6" s="3">
         <f t="shared" si="36"/>
@@ -9568,19 +9568,19 @@
       </c>
       <c r="AE7" s="4">
         <f>100*(AA7/TOTAL_BASIC!$C$81)</f>
-        <v>110.28367933911973</v>
+        <v>110.41881675690517</v>
       </c>
       <c r="AF7" s="4">
         <f>100*AC7/TOTAL_BASIC!$C$82</f>
-        <v>112.33103500664521</v>
+        <v>112.47625499369238</v>
       </c>
       <c r="AG7" s="4">
         <f>100*N7/TOTAL_BASIC!$C$87</f>
-        <v>111.48127208480565</v>
+        <v>111.8475352112676</v>
       </c>
       <c r="AH7" s="4">
         <f>100*AD7/TOTAL_BASIC!$C$86</f>
-        <v>105.93735218256624</v>
+        <v>106.02240150526755</v>
       </c>
       <c r="AI7" s="3">
         <f t="shared" si="36"/>
@@ -9808,19 +9808,19 @@
       </c>
       <c r="AE8" s="4">
         <f>100*(AA8/TOTAL_BASIC!$C$81)</f>
-        <v>110.00610038980638</v>
+        <v>110.14089767292579</v>
       </c>
       <c r="AF8" s="4">
         <f>100*AC8/TOTAL_BASIC!$C$82</f>
-        <v>103.54758856294538</v>
+        <v>103.6814534335841</v>
       </c>
       <c r="AG8" s="4">
         <f>100*N8/TOTAL_BASIC!$C$87</f>
-        <v>94.797879858657254</v>
+        <v>95.109330985915491</v>
       </c>
       <c r="AH8" s="4">
         <f>100*AD8/TOTAL_BASIC!$C$86</f>
-        <v>109.26327834765416</v>
+        <v>109.35099781230133</v>
       </c>
       <c r="AI8" s="3">
         <f t="shared" si="36"/>
@@ -10048,19 +10048,19 @@
       </c>
       <c r="AE9" s="4">
         <f>100*(AA9/TOTAL_BASIC!$C$81)</f>
-        <v>108.50024065191775</v>
+        <v>108.63319271190217</v>
       </c>
       <c r="AF9" s="4">
         <f>100*AC9/TOTAL_BASIC!$C$82</f>
-        <v>109.73270057939958</v>
+        <v>109.87456147613082</v>
       </c>
       <c r="AG9" s="4">
         <f>100*N9/TOTAL_BASIC!$C$87</f>
-        <v>114.58515901060071</v>
+        <v>114.96161971830986</v>
       </c>
       <c r="AH9" s="4">
         <f>100*AD9/TOTAL_BASIC!$C$86</f>
-        <v>101.85363616036955</v>
+        <v>101.93540696728169</v>
       </c>
       <c r="AI9" s="3">
         <f t="shared" si="36"/>
@@ -10288,19 +10288,19 @@
       </c>
       <c r="AE10" s="4">
         <f>100*(AA10/TOTAL_BASIC!$C$81)</f>
-        <v>102.88531191194028</v>
+        <v>103.01138365222992</v>
       </c>
       <c r="AF10" s="4">
         <f>100*AC10/TOTAL_BASIC!$C$82</f>
-        <v>110.28193914487819</v>
+        <v>110.42451008952595</v>
       </c>
       <c r="AG10" s="4">
         <f>100*N10/TOTAL_BASIC!$C$87</f>
-        <v>91.306007067137799</v>
+        <v>91.605985915492951</v>
       </c>
       <c r="AH10" s="4">
         <f>100*AD10/TOTAL_BASIC!$C$86</f>
-        <v>105.61405936184609</v>
+        <v>105.6988491364761</v>
       </c>
       <c r="AI10" s="3">
         <f t="shared" si="36"/>
@@ -10528,19 +10528,19 @@
       </c>
       <c r="AE11" s="4">
         <f>100*(AA11/TOTAL_BASIC!$C$81)</f>
-        <v>107.43171266820227</v>
+        <v>107.56335539471674</v>
       </c>
       <c r="AF11" s="4">
         <f>100*AC11/TOTAL_BASIC!$C$82</f>
-        <v>110.69833293216575</v>
+        <v>110.8414421848634</v>
       </c>
       <c r="AG11" s="4">
         <f>100*N11/TOTAL_BASIC!$C$87</f>
-        <v>100.61766784452297</v>
+        <v>100.94823943661972</v>
       </c>
       <c r="AH11" s="4">
         <f>100*AD11/TOTAL_BASIC!$C$86</f>
-        <v>111.44854391460727</v>
+        <v>111.53801776854738</v>
       </c>
       <c r="AI11" s="3">
         <f t="shared" si="36"/>
@@ -10768,19 +10768,19 @@
       </c>
       <c r="AE12" s="4">
         <f>100*(AA12/TOTAL_BASIC!$C$81)</f>
-        <v>106.9944429142742</v>
+        <v>107.12554982709641</v>
       </c>
       <c r="AF12" s="4">
         <f>100*AC12/TOTAL_BASIC!$C$82</f>
-        <v>105.95340887694945</v>
+        <v>106.09038395835776</v>
       </c>
       <c r="AG12" s="4">
         <f>100*N12/TOTAL_BASIC!$C$87</f>
-        <v>103.46289752650178</v>
+        <v>103.80281690140845</v>
       </c>
       <c r="AH12" s="4">
         <f>100*AD12/TOTAL_BASIC!$C$86</f>
-        <v>107.14551133103168</v>
+        <v>107.23153059601658</v>
       </c>
       <c r="AI12" s="3">
         <f t="shared" si="36"/>
@@ -11008,19 +11008,19 @@
       </c>
       <c r="AE13" s="4">
         <f>100*(AA13/TOTAL_BASIC!$C$81)</f>
-        <v>105.41025331294678</v>
+        <v>105.53941902020449</v>
       </c>
       <c r="AF13" s="4">
         <f>100*AC13/TOTAL_BASIC!$C$82</f>
-        <v>110.72893646173068</v>
+        <v>110.87208527824224</v>
       </c>
       <c r="AG13" s="4">
         <f>100*N13/TOTAL_BASIC!$C$87</f>
-        <v>77.597173144876322</v>
+        <v>77.852112676056336</v>
       </c>
       <c r="AH13" s="4">
         <f>100*AD13/TOTAL_BASIC!$C$86</f>
-        <v>107.01933218008472</v>
+        <v>107.10525014509273</v>
       </c>
       <c r="AI13" s="3">
         <f t="shared" si="36"/>
@@ -11248,19 +11248,19 @@
       </c>
       <c r="AE14" s="4">
         <f>100*(AA14/TOTAL_BASIC!$C$81)</f>
-        <v>101.66863705720763</v>
+        <v>101.79321793049741</v>
       </c>
       <c r="AF14" s="4">
         <f>100*AC14/TOTAL_BASIC!$C$82</f>
-        <v>107.67696139273703</v>
+        <v>107.81616465867157</v>
       </c>
       <c r="AG14" s="4">
         <f>100*N14/TOTAL_BASIC!$C$87</f>
-        <v>73.846643109540636</v>
+        <v>74.089260563380279</v>
       </c>
       <c r="AH14" s="4">
         <f>100*AD14/TOTAL_BASIC!$C$86</f>
-        <v>109.3623150137427</v>
+        <v>109.45011398765831</v>
       </c>
       <c r="AI14" s="3">
         <f t="shared" si="36"/>
@@ -11488,19 +11488,19 @@
       </c>
       <c r="AE15" s="4">
         <f>100*(AA15/TOTAL_BASIC!$C$81)</f>
-        <v>96.339504483987156</v>
+        <v>96.457555241313287</v>
       </c>
       <c r="AF15" s="4">
         <f>100*AC15/TOTAL_BASIC!$C$82</f>
-        <v>98.652751068939281</v>
+        <v>98.780287962296953</v>
       </c>
       <c r="AG15" s="4">
         <f>100*N15/TOTAL_BASIC!$C$87</f>
-        <v>109.92932862190813</v>
+        <v>110.29049295774648</v>
       </c>
       <c r="AH15" s="4">
         <f>100*AD15/TOTAL_BASIC!$C$86</f>
-        <v>95.527323355377646</v>
+        <v>95.60401523018345</v>
       </c>
       <c r="AI15" s="3">
         <f t="shared" si="36"/>
@@ -11728,19 +11728,19 @@
       </c>
       <c r="AE16" s="4">
         <f>100*(AA16/TOTAL_BASIC!$C$81)</f>
-        <v>99.809006904606505</v>
+        <v>99.931309057977217</v>
       </c>
       <c r="AF16" s="4">
         <f>100*AC16/TOTAL_BASIC!$C$82</f>
-        <v>100.86776597828377</v>
+        <v>100.9981664118592</v>
       </c>
       <c r="AG16" s="4">
         <f>100*N16/TOTAL_BASIC!$C$87</f>
-        <v>116.39575971731449</v>
+        <v>116.77816901408451</v>
       </c>
       <c r="AH16" s="4">
         <f>100*AD16/TOTAL_BASIC!$C$86</f>
-        <v>100.40828148302469</v>
+        <v>100.48889192077678</v>
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="36"/>
@@ -11968,19 +11968,19 @@
       </c>
       <c r="AE17" s="4">
         <f>100*(AA17/TOTAL_BASIC!$C$81)</f>
-        <v>110.47502402311748</v>
+        <v>110.61039590738662</v>
       </c>
       <c r="AF17" s="4">
         <f>100*AC17/TOTAL_BASIC!$C$82</f>
-        <v>109.49174164092923</v>
+        <v>109.63329102932335</v>
       </c>
       <c r="AG17" s="4">
         <f>100*N17/TOTAL_BASIC!$C$87</f>
-        <v>86.262190812720846</v>
+        <v>86.545598591549293</v>
       </c>
       <c r="AH17" s="4">
         <f>100*AD17/TOTAL_BASIC!$C$86</f>
-        <v>109.64875376443348</v>
+        <v>109.73678269899318</v>
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="36"/>
@@ -12208,19 +12208,19 @@
       </c>
       <c r="AE18" s="4">
         <f>100*(AA18/TOTAL_BASIC!$C$81)</f>
-        <v>105.86581861295204</v>
+        <v>105.99554255256693</v>
       </c>
       <c r="AF18" s="4">
         <f>100*AC18/TOTAL_BASIC!$C$82</f>
-        <v>101.87788934207894</v>
+        <v>102.009595648976</v>
       </c>
       <c r="AG18" s="4">
         <f>100*N18/TOTAL_BASIC!$C$87</f>
-        <v>106.56678445229683</v>
+        <v>106.9169014084507</v>
       </c>
       <c r="AH18" s="4">
         <f>100*AD18/TOTAL_BASIC!$C$86</f>
-        <v>107.65777711479069</v>
+        <v>107.74420764036549</v>
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="36"/>
@@ -12448,19 +12448,19 @@
       </c>
       <c r="AE19" s="4">
         <f>100*(AA19/TOTAL_BASIC!$C$81)</f>
-        <v>91.796876432200818</v>
+        <v>91.909360826230426</v>
       </c>
       <c r="AF19" s="4">
         <f>100*AC19/TOTAL_BASIC!$C$82</f>
-        <v>93.759867181228202</v>
+        <v>93.881078622899665</v>
       </c>
       <c r="AG19" s="4">
         <f>100*N19/TOTAL_BASIC!$C$87</f>
-        <v>106.56678445229683</v>
+        <v>106.9169014084507</v>
       </c>
       <c r="AH19" s="4">
         <f>100*AD19/TOTAL_BASIC!$C$86</f>
-        <v>89.556865645666548</v>
+        <v>89.628764278296984</v>
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="36"/>
@@ -12688,19 +12688,19 @@
       </c>
       <c r="AE20" s="4">
         <f>100*(AA20/TOTAL_BASIC!$C$81)</f>
-        <v>88.704968371713306</v>
+        <v>88.813664059437244</v>
       </c>
       <c r="AF20" s="4">
         <f>100*AC20/TOTAL_BASIC!$C$82</f>
-        <v>88.809414476165628</v>
+        <v>88.924226041990977</v>
       </c>
       <c r="AG20" s="4">
         <f>100*N20/TOTAL_BASIC!$C$87</f>
-        <v>114.45583038869259</v>
+        <v>114.8318661971831</v>
       </c>
       <c r="AH20" s="4">
         <f>100*AD20/TOTAL_BASIC!$C$86</f>
-        <v>76.952566036276437</v>
+        <v>77.014345602092234</v>
       </c>
       <c r="AI20" s="3">
         <f t="shared" si="36"/>
@@ -12928,19 +12928,19 @@
       </c>
       <c r="AE21" s="4">
         <f>100*(AA21/TOTAL_BASIC!$C$81)</f>
-        <v>95.333079101256601</v>
+        <v>95.44989662327329</v>
       </c>
       <c r="AF21" s="4">
         <f>100*AC21/TOTAL_BASIC!$C$82</f>
-        <v>98.105049246918668</v>
+        <v>98.231878079040243</v>
       </c>
       <c r="AG21" s="4">
         <f>100*N21/TOTAL_BASIC!$C$87</f>
-        <v>114.0678445229682</v>
+        <v>114.44260563380281</v>
       </c>
       <c r="AH21" s="4">
         <f>100*AD21/TOTAL_BASIC!$C$86</f>
-        <v>94.83004362285665</v>
+        <v>94.906175702955835</v>
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="36"/>
@@ -13168,19 +13168,19 @@
       </c>
       <c r="AE22" s="4">
         <f>100*(AA22/TOTAL_BASIC!$C$81)</f>
-        <v>100.67676893970234</v>
+        <v>100.8001344156007</v>
       </c>
       <c r="AF22" s="4">
         <f>100*AC22/TOTAL_BASIC!$C$82</f>
-        <v>99.182556637593834</v>
+        <v>99.310778456162183</v>
       </c>
       <c r="AG22" s="4">
         <f>100*N22/TOTAL_BASIC!$C$87</f>
-        <v>111.73992932862191</v>
+        <v>112.10704225352113</v>
       </c>
       <c r="AH22" s="4">
         <f>100*AD22/TOTAL_BASIC!$C$86</f>
-        <v>94.689364378576087</v>
+        <v>94.765383517637986</v>
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="36"/>
@@ -13408,19 +13408,19 @@
       </c>
       <c r="AE23" s="4">
         <f>100*(AA23/TOTAL_BASIC!$C$81)</f>
-        <v>92.844880584937144</v>
+        <v>92.958649163316394</v>
       </c>
       <c r="AF23" s="4">
         <f>100*AC23/TOTAL_BASIC!$C$82</f>
-        <v>94.177368085424803</v>
+        <v>94.299119266411367</v>
       </c>
       <c r="AG23" s="4">
         <f>100*N23/TOTAL_BASIC!$C$87</f>
-        <v>101.65229681978798</v>
+        <v>101.98626760563378</v>
       </c>
       <c r="AH23" s="4">
         <f>100*AD23/TOTAL_BASIC!$C$86</f>
-        <v>94.76916999541433</v>
+        <v>94.845253204547078</v>
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="36"/>
@@ -13648,19 +13648,19 @@
       </c>
       <c r="AE24" s="4">
         <f>100*(AA24/TOTAL_BASIC!$C$81)</f>
-        <v>112.94177097100209</v>
+        <v>113.08016551297419</v>
       </c>
       <c r="AF24" s="4">
         <f>100*AC24/TOTAL_BASIC!$C$82</f>
-        <v>115.12734599009471</v>
+        <v>115.2761810087738</v>
       </c>
       <c r="AG24" s="4">
         <f>100*N24/TOTAL_BASIC!$C$87</f>
-        <v>64.664310954063609</v>
+        <v>64.876760563380287</v>
       </c>
       <c r="AH24" s="4">
         <f>100*AD24/TOTAL_BASIC!$C$86</f>
-        <v>127.36976447383687</v>
+        <v>127.47202030691128</v>
       </c>
       <c r="AI24" s="3">
         <f t="shared" si="36"/>
@@ -13888,19 +13888,19 @@
       </c>
       <c r="AE25" s="4">
         <f>100*(AA25/TOTAL_BASIC!$C$81)</f>
-        <v>118.99031131210319</v>
+        <v>119.13611750490128</v>
       </c>
       <c r="AF25" s="4">
         <f>100*AC25/TOTAL_BASIC!$C$82</f>
-        <v>115.74198890503156</v>
+        <v>115.8916185254531</v>
       </c>
       <c r="AG25" s="4">
         <f>100*N25/TOTAL_BASIC!$C$87</f>
-        <v>86.262190812720846</v>
+        <v>86.545598591549293</v>
       </c>
       <c r="AH25" s="4">
         <f>100*AD25/TOTAL_BASIC!$C$86</f>
-        <v>126.57370344587538</v>
+        <v>126.67532017999308</v>
       </c>
       <c r="AI25" s="3">
         <f t="shared" si="36"/>
@@ -14128,19 +14128,19 @@
       </c>
       <c r="AE26" s="4">
         <f>100*(AA26/TOTAL_BASIC!$C$81)</f>
-        <v>94.379581760490169</v>
+        <v>94.49523090320298</v>
       </c>
       <c r="AF26" s="4">
         <f>100*AC26/TOTAL_BASIC!$C$82</f>
-        <v>94.139625654936765</v>
+        <v>94.261328043038375</v>
       </c>
       <c r="AG26" s="4">
         <f>100*N26/TOTAL_BASIC!$C$87</f>
-        <v>74.622614840989399</v>
+        <v>74.867781690140845</v>
       </c>
       <c r="AH26" s="4">
         <f>100*AD26/TOTAL_BASIC!$C$86</f>
-        <v>91.462330872170085</v>
+        <v>91.535759262941596</v>
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="36"/>
@@ -14368,19 +14368,19 @@
       </c>
       <c r="AE27" s="4">
         <f>100*(AA27/TOTAL_BASIC!$C$81)</f>
-        <v>104.97228669902231</v>
+        <v>105.10091573868208</v>
       </c>
       <c r="AF27" s="4">
         <f>100*AC27/TOTAL_BASIC!$C$82</f>
-        <v>109.53580270396384</v>
+        <v>109.67740905388246</v>
       </c>
       <c r="AG27" s="4">
         <f>100*N27/TOTAL_BASIC!$C$87</f>
-        <v>129.32862190812722</v>
+        <v>129.75352112676057</v>
       </c>
       <c r="AH27" s="4">
         <f>100*AD27/TOTAL_BASIC!$C$86</f>
-        <v>103.12608771319177</v>
+        <v>103.20888007803894</v>
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="36"/>
@@ -14608,19 +14608,19 @@
       </c>
       <c r="AE28" s="4">
         <f>100*(AA28/TOTAL_BASIC!$C$81)</f>
-        <v>91.821122833794107</v>
+        <v>91.933636938440202</v>
       </c>
       <c r="AF28" s="4">
         <f>100*AC28/TOTAL_BASIC!$C$82</f>
-        <v>97.289595414677592</v>
+        <v>97.415370039518436</v>
       </c>
       <c r="AG28" s="4">
         <f>100*N28/TOTAL_BASIC!$C$87</f>
-        <v>129.32862190812722</v>
+        <v>129.75352112676057</v>
       </c>
       <c r="AH28" s="4">
         <f>100*AD28/TOTAL_BASIC!$C$86</f>
-        <v>91.588052289176517</v>
+        <v>91.661581612443939</v>
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="36"/>
@@ -14848,19 +14848,19 @@
       </c>
       <c r="AE29" s="4">
         <f>100*(AA29/TOTAL_BASIC!$C$81)</f>
-        <v>94.157473082803676</v>
+        <v>94.272850062007336</v>
       </c>
       <c r="AF29" s="4">
         <f>100*AC29/TOTAL_BASIC!$C$82</f>
-        <v>96.61036027140814</v>
+        <v>96.735256790579413</v>
       </c>
       <c r="AG29" s="4">
         <f>100*N29/TOTAL_BASIC!$C$87</f>
-        <v>112.1279151943463</v>
+        <v>112.49630281690141</v>
       </c>
       <c r="AH29" s="4">
         <f>100*AD29/TOTAL_BASIC!$C$86</f>
-        <v>89.158835131685791</v>
+        <v>89.230414214837879</v>
       </c>
       <c r="AI29" s="3">
         <f t="shared" si="36"/>
@@ -15088,19 +15088,19 @@
       </c>
       <c r="AE30" s="4">
         <f>100*(AA30/TOTAL_BASIC!$C$81)</f>
-        <v>110.15881152202462</v>
+        <v>110.29379593154567</v>
       </c>
       <c r="AF30" s="4">
         <f>100*AC30/TOTAL_BASIC!$C$82</f>
-        <v>99.414705575750844</v>
+        <v>99.543227513211448</v>
       </c>
       <c r="AG30" s="4">
         <f>100*N30/TOTAL_BASIC!$C$87</f>
-        <v>84.063604240282686</v>
+        <v>84.339788732394368</v>
       </c>
       <c r="AH30" s="4">
         <f>100*AD30/TOTAL_BASIC!$C$86</f>
-        <v>105.08005569091542</v>
+        <v>105.16441675320179</v>
       </c>
       <c r="AI30" s="3">
         <f t="shared" si="36"/>
@@ -15328,19 +15328,19 @@
       </c>
       <c r="AE31" s="4">
         <f>100*(AA31/TOTAL_BASIC!$C$81)</f>
-        <v>97.779573398216939</v>
+        <v>97.899388761109975</v>
       </c>
       <c r="AF31" s="4">
         <f>100*AC31/TOTAL_BASIC!$C$82</f>
-        <v>94.683052999721554</v>
+        <v>94.805457923075053</v>
       </c>
       <c r="AG31" s="4">
         <f>100*N31/TOTAL_BASIC!$C$87</f>
-        <v>110.83462897526502</v>
+        <v>111.1987676056338</v>
       </c>
       <c r="AH31" s="4">
         <f>100*AD31/TOTAL_BASIC!$C$86</f>
-        <v>99.15494322963248</v>
+        <v>99.234547454114463</v>
       </c>
       <c r="AI31" s="3">
         <f t="shared" si="36"/>
@@ -15568,19 +15568,19 @@
       </c>
       <c r="AE32" s="4">
         <f>100*(AA32/TOTAL_BASIC!$C$81)</f>
-        <v>98.309413451113642</v>
+        <v>98.429878059815465</v>
       </c>
       <c r="AF32" s="4">
         <f>100*AC32/TOTAL_BASIC!$C$82</f>
-        <v>97.188765031384477</v>
+        <v>97.314409304119565</v>
       </c>
       <c r="AG32" s="4">
         <f>100*N32/TOTAL_BASIC!$C$87</f>
-        <v>107.73074204946997</v>
+        <v>108.08468309859155</v>
       </c>
       <c r="AH32" s="4">
         <f>100*AD32/TOTAL_BASIC!$C$86</f>
-        <v>105.20097635339059</v>
+        <v>105.2854344939995</v>
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="36"/>
@@ -15808,19 +15808,19 @@
       </c>
       <c r="AE33" s="4">
         <f>100*(AA33/TOTAL_BASIC!$C$81)</f>
-        <v>89.653238681833216</v>
+        <v>89.763096343856887</v>
       </c>
       <c r="AF33" s="4">
         <f>100*AC33/TOTAL_BASIC!$C$82</f>
-        <v>94.284555301911297</v>
+        <v>94.406445053028449</v>
       </c>
       <c r="AG33" s="4">
         <f>100*N33/TOTAL_BASIC!$C$87</f>
-        <v>95.315194346289758</v>
+        <v>95.62834507042254</v>
       </c>
       <c r="AH33" s="4">
         <f>100*AD33/TOTAL_BASIC!$C$86</f>
-        <v>85.042617133445972</v>
+        <v>85.110891607358454</v>
       </c>
       <c r="AI33" s="3">
         <f t="shared" si="36"/>
@@ -16048,11 +16048,11 @@
       </c>
       <c r="AE34" s="4">
         <f>100*(AA34/TOTAL_BASIC!$C$81)</f>
-        <v>96.565214180206794</v>
+        <v>96.683541513592942</v>
       </c>
       <c r="AF34" s="4">
         <f>100*AC34/TOTAL_BASIC!$C$82</f>
-        <v>86.717459379615946</v>
+        <v>86.829566495224086</v>
       </c>
       <c r="AG34" s="4">
         <f>100*N34/TOTAL_BASIC!$C$87</f>
@@ -16060,7 +16060,7 @@
       </c>
       <c r="AH34" s="4">
         <f>100*AD34/TOTAL_BASIC!$C$86</f>
-        <v>107.46823877479986</v>
+        <v>107.55451713395638</v>
       </c>
       <c r="AI34" s="3">
         <f t="shared" si="36"/>
@@ -16288,19 +16288,19 @@
       </c>
       <c r="AE35" s="4">
         <f>100*(AA35/TOTAL_BASIC!$C$81)</f>
-        <v>90.772117258538273</v>
+        <v>90.883345951729737</v>
       </c>
       <c r="AF35" s="4">
         <f>100*AC35/TOTAL_BASIC!$C$82</f>
-        <v>89.178381918859998</v>
+        <v>89.293670480621927</v>
       </c>
       <c r="AG35" s="4">
         <f>100*N35/TOTAL_BASIC!$C$87</f>
-        <v>76.045229681978796</v>
+        <v>76.295070422535204</v>
       </c>
       <c r="AH35" s="4">
         <f>100*AD35/TOTAL_BASIC!$C$86</f>
-        <v>90.62848626023009</v>
+        <v>90.701245218379185</v>
       </c>
       <c r="AI35" s="3">
         <f t="shared" si="36"/>
@@ -16528,19 +16528,19 @@
       </c>
       <c r="AE36" s="4">
         <f>100*(AA36/TOTAL_BASIC!$C$81)</f>
-        <v>128.90527216831686</v>
+        <v>129.06322777629208</v>
       </c>
       <c r="AF36" s="4">
         <f>100*AC36/TOTAL_BASIC!$C$82</f>
-        <v>117.67215911984923</v>
+        <v>117.82428403726129</v>
       </c>
       <c r="AG36" s="4">
         <f>100*N36/TOTAL_BASIC!$C$87</f>
-        <v>106.56678445229683</v>
+        <v>106.9169014084507</v>
       </c>
       <c r="AH36" s="4">
         <f>100*AD36/TOTAL_BASIC!$C$86</f>
-        <v>118.45388096066829</v>
+        <v>118.54897888542749</v>
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="36"/>
@@ -16768,19 +16768,19 @@
       </c>
       <c r="AE37" s="4">
         <f>100*(AA37/TOTAL_BASIC!$C$81)</f>
-        <v>99.446774327900798</v>
+        <v>99.56863261527657</v>
       </c>
       <c r="AF37" s="4">
         <f>100*AC37/TOTAL_BASIC!$C$82</f>
-        <v>100.41784039996824</v>
+        <v>100.5476591760645</v>
       </c>
       <c r="AG37" s="4">
         <f>100*N37/TOTAL_BASIC!$C$87</f>
-        <v>55.481978798586574</v>
+        <v>55.664260563380282</v>
       </c>
       <c r="AH37" s="4">
         <f>100*AD37/TOTAL_BASIC!$C$86</f>
-        <v>107.9874090104269</v>
+        <v>108.07410417325086</v>
       </c>
       <c r="AI37" s="3">
         <f t="shared" si="36"/>
@@ -17008,19 +17008,19 @@
       </c>
       <c r="AE38" s="4">
         <f>100*(AA38/TOTAL_BASIC!$C$81)</f>
-        <v>81.438089125200747</v>
+        <v>81.537880256034526</v>
       </c>
       <c r="AF38" s="4">
         <f>100*AC38/TOTAL_BASIC!$C$82</f>
-        <v>79.204876813824683</v>
+        <v>79.307271768026752</v>
       </c>
       <c r="AG38" s="4">
         <f>100*N38/TOTAL_BASIC!$C$87</f>
-        <v>43.066431095406358</v>
+        <v>43.20792253521126</v>
       </c>
       <c r="AH38" s="4">
         <f>100*AD38/TOTAL_BASIC!$C$86</f>
-        <v>90.923596928612454</v>
+        <v>90.996592809451712</v>
       </c>
       <c r="AI38" s="3">
         <f t="shared" si="36"/>
@@ -17248,19 +17248,19 @@
       </c>
       <c r="AE39" s="4">
         <f>100*(AA39/TOTAL_BASIC!$C$81)</f>
-        <v>79.856729283886025</v>
+        <v>79.954582676635383</v>
       </c>
       <c r="AF39" s="4">
         <f>100*AC39/TOTAL_BASIC!$C$82</f>
-        <v>82.733522085352078</v>
+        <v>82.84047882268554</v>
       </c>
       <c r="AG39" s="4">
         <f>100*N39/TOTAL_BASIC!$C$87</f>
-        <v>94.021908127208491</v>
+        <v>94.330809859154925</v>
       </c>
       <c r="AH39" s="4">
         <f>100*AD39/TOTAL_BASIC!$C$86</f>
-        <v>76.18001735935178</v>
+        <v>76.241176702551343</v>
       </c>
       <c r="AI39" s="3">
         <f t="shared" si="36"/>
@@ -17488,19 +17488,19 @@
       </c>
       <c r="AE40" s="4">
         <f>100*(AA40/TOTAL_BASIC!$C$81)</f>
-        <v>89.766042953775539</v>
+        <v>89.87603884185512</v>
       </c>
       <c r="AF40" s="4">
         <f>100*AC40/TOTAL_BASIC!$C$82</f>
-        <v>87.207708117139333</v>
+        <v>87.320449019441483</v>
       </c>
       <c r="AG40" s="4">
         <f>100*N40/TOTAL_BASIC!$C$87</f>
-        <v>96.996466431095413</v>
+        <v>97.315140845070417</v>
       </c>
       <c r="AH40" s="4">
         <f>100*AD40/TOTAL_BASIC!$C$86</f>
-        <v>95.527323355377646</v>
+        <v>95.60401523018345</v>
       </c>
       <c r="AI40" s="3">
         <f t="shared" si="36"/>
@@ -17728,19 +17728,19 @@
       </c>
       <c r="AE41" s="4">
         <f>100*(AA41/TOTAL_BASIC!$C$81)</f>
-        <v>98.49025090238986</v>
+        <v>98.610937102412819</v>
       </c>
       <c r="AF41" s="4">
         <f>100*AC41/TOTAL_BASIC!$C$82</f>
-        <v>92.809112003869956</v>
+        <v>92.929094322578791</v>
       </c>
       <c r="AG41" s="4">
         <f>100*N41/TOTAL_BASIC!$C$87</f>
-        <v>57.421908127208482</v>
+        <v>57.61056338028169</v>
       </c>
       <c r="AH41" s="4">
         <f>100*AD41/TOTAL_BASIC!$C$86</f>
-        <v>106.14147039486404</v>
+        <v>106.22668358909272</v>
       </c>
       <c r="AI41" s="3">
         <f t="shared" si="36"/>
@@ -17968,19 +17968,19 @@
       </c>
       <c r="AE42" s="4">
         <f>100*(AA42/TOTAL_BASIC!$C$81)</f>
-        <v>107.12986724207956</v>
+        <v>107.26114009871208</v>
       </c>
       <c r="AF42" s="4">
         <f>100*AC42/TOTAL_BASIC!$C$82</f>
-        <v>102.5364705609226</v>
+        <v>102.66902827238532</v>
       </c>
       <c r="AG42" s="4">
         <f>100*N42/TOTAL_BASIC!$C$87</f>
-        <v>64.664310954063609</v>
+        <v>64.876760563380287</v>
       </c>
       <c r="AH42" s="4">
         <f>100*AD42/TOTAL_BASIC!$C$86</f>
-        <v>115.02269546872003</v>
+        <v>115.11503874654743</v>
       </c>
       <c r="AI42" s="3">
         <f t="shared" si="36"/>
@@ -18208,19 +18208,19 @@
       </c>
       <c r="AE43" s="4">
         <f>100*(AA43/TOTAL_BASIC!$C$81)</f>
-        <v>82.894334083389708</v>
+        <v>82.995909641298198</v>
       </c>
       <c r="AF43" s="4">
         <f>100*AC43/TOTAL_BASIC!$C$82</f>
-        <v>80.510369594731785</v>
+        <v>80.614452271696507</v>
       </c>
       <c r="AG43" s="4">
         <f>100*N43/TOTAL_BASIC!$C$87</f>
-        <v>64.664310954063609</v>
+        <v>64.876760563380287</v>
       </c>
       <c r="AH43" s="4">
         <f>100*AD43/TOTAL_BASIC!$C$86</f>
-        <v>84.741980395899517</v>
+        <v>84.810013510646598</v>
       </c>
       <c r="AI43" s="3">
         <f t="shared" si="36"/>
@@ -18448,19 +18448,19 @@
       </c>
       <c r="AE44" s="4">
         <f>100*(AA44/TOTAL_BASIC!$C$81)</f>
-        <v>77.916376521066326</v>
+        <v>78.011852279486376</v>
       </c>
       <c r="AF44" s="4">
         <f>100*AC44/TOTAL_BASIC!$C$82</f>
-        <v>76.133635897475145</v>
+        <v>76.232060394482872</v>
       </c>
       <c r="AG44" s="4">
         <f>100*N44/TOTAL_BASIC!$C$87</f>
-        <v>43.066431095406358</v>
+        <v>43.20792253521126</v>
       </c>
       <c r="AH44" s="4">
         <f>100*AD44/TOTAL_BASIC!$C$86</f>
-        <v>83.770114327023464</v>
+        <v>83.837367201853169</v>
       </c>
       <c r="AI44" s="3">
         <f t="shared" si="36"/>
@@ -18688,11 +18688,11 @@
       </c>
       <c r="AE45" s="4">
         <f>100*(AA45/TOTAL_BASIC!$C$81)</f>
-        <v>73.573496518252796</v>
+        <v>73.663650677023185</v>
       </c>
       <c r="AF45" s="4">
         <f>100*AC45/TOTAL_BASIC!$C$82</f>
-        <v>72.264549483013298</v>
+        <v>72.357972079353402</v>
       </c>
       <c r="AG45" s="4">
         <f>100*N45/TOTAL_BASIC!$C$87</f>
@@ -18700,7 +18700,7 @@
       </c>
       <c r="AH45" s="4">
         <f>100*AD45/TOTAL_BASIC!$C$86</f>
-        <v>81.88056287603797</v>
+        <v>81.946298768728667</v>
       </c>
       <c r="AI45" s="3">
         <f t="shared" si="36"/>
@@ -18928,19 +18928,19 @@
       </c>
       <c r="AE46" s="4">
         <f>100*(AA46/TOTAL_BASIC!$C$81)</f>
-        <v>88.438851763451893</v>
+        <v>88.547221362025681</v>
       </c>
       <c r="AF46" s="4">
         <f>100*AC46/TOTAL_BASIC!$C$82</f>
-        <v>93.804093132493392</v>
+        <v>93.925361748854542</v>
       </c>
       <c r="AG46" s="4">
         <f>100*N46/TOTAL_BASIC!$C$87</f>
-        <v>129.32862190812722</v>
+        <v>129.75352112676057</v>
       </c>
       <c r="AH46" s="4">
         <f>100*AD46/TOTAL_BASIC!$C$86</f>
-        <v>93.654238583703574</v>
+        <v>93.729426696258287</v>
       </c>
       <c r="AI46" s="3">
         <f t="shared" si="36"/>
@@ -19168,19 +19168,19 @@
       </c>
       <c r="AE47" s="4">
         <f>100*(AA47/TOTAL_BASIC!$C$81)</f>
-        <v>64.500849548757273</v>
+        <v>64.579886431687001</v>
       </c>
       <c r="AF47" s="4">
         <f>100*AC47/TOTAL_BASIC!$C$82</f>
-        <v>60.220457902511079</v>
+        <v>60.29831006612784</v>
       </c>
       <c r="AG47" s="4">
         <f>100*N47/TOTAL_BASIC!$C$87</f>
-        <v>86.262190812720846</v>
+        <v>86.545598591549293</v>
       </c>
       <c r="AH47" s="4">
         <f>100*AD47/TOTAL_BASIC!$C$86</f>
-        <v>65.585923497721978</v>
+        <v>65.63857762072297</v>
       </c>
       <c r="AI47" s="3">
         <f t="shared" si="36"/>
@@ -19408,11 +19408,11 @@
       </c>
       <c r="AE48" s="4">
         <f>100*(AA48/TOTAL_BASIC!$C$81)</f>
-        <v>61.311247098543994</v>
+        <v>61.386375564186004</v>
       </c>
       <c r="AF48" s="4">
         <f>100*AC48/TOTAL_BASIC!$C$82</f>
-        <v>60.220457902511079</v>
+        <v>60.29831006612784</v>
       </c>
       <c r="AG48" s="4">
         <f>100*N48/TOTAL_BASIC!$C$87</f>
@@ -19420,7 +19420,7 @@
       </c>
       <c r="AH48" s="4">
         <f>100*AD48/TOTAL_BASIC!$C$86</f>
-        <v>68.233802396698323</v>
+        <v>68.288582307273899</v>
       </c>
       <c r="AI48" s="3">
         <f t="shared" si="36"/>
@@ -19648,11 +19648,11 @@
       </c>
       <c r="AE49" s="4">
         <f>100*(AA49/TOTAL_BASIC!$C$81)</f>
-        <v>91.314623338257022</v>
+        <v>91.426516797723821</v>
       </c>
       <c r="AF49" s="4">
         <f>100*AC49/TOTAL_BASIC!$C$82</f>
-        <v>96.352732644017721</v>
+        <v>96.477296105804541</v>
       </c>
       <c r="AG49" s="4">
         <f>100*N49/TOTAL_BASIC!$C$87</f>
@@ -19660,7 +19660,7 @@
       </c>
       <c r="AH49" s="4">
         <f>100*AD49/TOTAL_BASIC!$C$86</f>
-        <v>99.592315838585193</v>
+        <v>99.672271197425289</v>
       </c>
       <c r="AI49" s="3">
         <f t="shared" si="36"/>
@@ -19888,11 +19888,11 @@
       </c>
       <c r="AE50" s="4">
         <f>100*(AA50/TOTAL_BASIC!$C$81)</f>
-        <v>101.49496985907625</v>
+        <v>101.61933792719981</v>
       </c>
       <c r="AF50" s="4">
         <f>100*AC50/TOTAL_BASIC!$C$82</f>
-        <v>101.66416665712467</v>
+        <v>101.79559666633125</v>
       </c>
       <c r="AG50" s="4">
         <f>100*N50/TOTAL_BASIC!$C$87</f>
@@ -19900,7 +19900,7 @@
       </c>
       <c r="AH50" s="4">
         <f>100*AD50/TOTAL_BASIC!$C$86</f>
-        <v>116.49673579924104</v>
+        <v>116.59026247583348</v>
       </c>
       <c r="AI50" s="3">
         <f t="shared" si="36"/>
@@ -20130,19 +20130,19 @@
       </c>
       <c r="AE51" s="4">
         <f>100*(AA51/TOTAL_BASIC!$C$81)</f>
-        <v>99.268702241244952</v>
+        <v>99.390342325872012</v>
       </c>
       <c r="AF51" s="4">
         <f>100*AC51/TOTAL_BASIC!$C$82</f>
-        <v>103.77127484575695</v>
+        <v>103.90542889488574</v>
       </c>
       <c r="AG51" s="4">
         <f>100*N51/TOTAL_BASIC!$C$87</f>
-        <v>129.32862190812722</v>
+        <v>129.75352112676057</v>
       </c>
       <c r="AH51" s="4">
         <f>100*AD51/TOTAL_BASIC!$C$86</f>
-        <v>90.499569494568306</v>
+        <v>90.572224954910652</v>
       </c>
       <c r="AI51" s="3">
         <f t="shared" si="36"/>
@@ -20372,11 +20372,11 @@
       </c>
       <c r="AE52" s="4">
         <f>100*(AA52/TOTAL_BASIC!$C$81)</f>
-        <v>81.226608171926685</v>
+        <v>81.326140162059787</v>
       </c>
       <c r="AF52" s="4">
         <f>100*AC52/TOTAL_BASIC!$C$82</f>
-        <v>72.130353476545309</v>
+        <v>72.223602586169832</v>
       </c>
       <c r="AG52" s="4">
         <f>100*N52/TOTAL_BASIC!$C$87</f>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="AH52" s="4">
         <f>100*AD52/TOTAL_BASIC!$C$86</f>
-        <v>89.158835131685791</v>
+        <v>89.230414214837879</v>
       </c>
       <c r="AI52" s="3">
         <f t="shared" si="36"/>
@@ -20612,19 +20612,19 @@
       </c>
       <c r="AE53" s="4">
         <f>100*(AA53/TOTAL_BASIC!$C$81)</f>
-        <v>69.222375756420647</v>
+        <v>69.307198217629349</v>
       </c>
       <c r="AF53" s="4">
         <f>100*AC53/TOTAL_BASIC!$C$82</f>
-        <v>65.432209470826947</v>
+        <v>65.516799313796511</v>
       </c>
       <c r="AG53" s="4">
         <f>100*N53/TOTAL_BASIC!$C$87</f>
-        <v>129.32862190812722</v>
+        <v>129.75352112676057</v>
       </c>
       <c r="AH53" s="4">
         <f>100*AD53/TOTAL_BASIC!$C$86</f>
-        <v>66.134300784492211</v>
+        <v>66.187395159357777</v>
       </c>
       <c r="AI53" s="3">
         <f t="shared" si="36"/>
@@ -20852,15 +20852,15 @@
       </c>
       <c r="AE54" s="4">
         <f>100*(AA54/TOTAL_BASIC!$C$81)</f>
-        <v>32.269077420286315</v>
+        <v>32.30861871799263</v>
       </c>
       <c r="AF54" s="4">
         <f>100*AC54/TOTAL_BASIC!$C$82</f>
-        <v>36.222831821059295</v>
+        <v>36.269660190152081</v>
       </c>
       <c r="AG54" s="4">
         <f>100*N54/TOTAL_BASIC!$C$87</f>
-        <v>43.066431095406358</v>
+        <v>43.20792253521126</v>
       </c>
       <c r="AH54" s="4">
         <f>100*AD54/TOTAL_BASIC!$C$86</f>
@@ -21965,7 +21965,7 @@
         <v>17.299999999999997</v>
       </c>
       <c r="L4" s="4">
-        <f t="shared" ref="L4:L58" si="2">100-((PERCENTRANK(E$3:E$49,E4))*100)</f>
+        <f t="shared" ref="L4:L57" si="2">100-((PERCENTRANK(E$3:E$49,E4))*100)</f>
         <v>15.299999999999997</v>
       </c>
       <c r="M4" s="4">
